--- a/tiflow/ti-flow-system-diagram/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/ti-flow-system-diagram/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:00:56+00:00</t>
+    <t>2026-06-12T12:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/ti-flow-system-diagram/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/ti-flow-system-diagram/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:16:50+00:00</t>
+    <t>2026-06-17T07:52:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/ti-flow-system-diagram/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/ti-flow-system-diagram/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:52:30+00:00</t>
+    <t>2026-06-18T06:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
